--- a/questionnaire_templates/014_environmental_impact_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/014_environmental_impact_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very low</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>reduce_carbon_footprint</t>
+          <t>reduce carbon footprint</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>improve_public_health</t>
+          <t>improve public health</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>create_jobs</t>
+          <t>create jobs</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>reduce_cost</t>
+          <t>reduce cost</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very low</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>more_sustainability</t>
+          <t>more sustainability</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>more_community_involvement</t>
+          <t>more community involvement</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>more_transparency</t>
+          <t>more transparency</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>more_responsibility</t>
+          <t>more responsibility</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>very_uneffective</t>
+          <t>very uneffective</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>somewhat_effective</t>
+          <t>somewhat effective</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>very_effective</t>
+          <t>very effective</t>
         </is>
       </c>
     </row>
